--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria-Melania\Desktop\CheckLists\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria-Melania\OneDrive\Documents\Proiect VVSS\VVSS-MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" tabRatio="650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Se menționează Java și JavaFX, dar nu este specificată versiunea minimă necesară.</t>
+  </si>
+  <si>
+    <t>60 min</t>
   </si>
 </sst>
 </file>
@@ -414,6 +417,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -456,7 +460,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,19 +785,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -807,10 +810,10 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="36" t="s">
+      <c r="J3" s="22" t="s">
         <v>36</v>
       </c>
     </row>
@@ -818,17 +821,17 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="26"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="22" t="s">
         <v>36</v>
       </c>
     </row>
@@ -836,17 +839,17 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="28"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="I5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="36" t="s">
+      <c r="J5" s="22" t="s">
         <v>36</v>
       </c>
     </row>
@@ -855,19 +858,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1055,7 +1058,9 @@
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1093,19 +1098,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1125,10 +1130,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1139,10 +1144,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1154,15 +1159,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1374,19 +1379,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1406,10 +1411,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1420,10 +1425,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="34"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1435,15 +1440,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1692,19 +1697,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1724,8 +1729,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1736,8 +1741,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1749,8 +1754,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1980,11 +1985,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -188,19 +188,65 @@
   </si>
   <si>
     <t>60 min</t>
+  </si>
+  <si>
+    <t>13.03.2026</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>Modelul inițial nu includea unitateea de măsură pentru ingrediente./A fost adăugat enum-ul UnitateMasura în relația cu IngredientReteta.</t>
+  </si>
+  <si>
+    <t>Unele relații nu aveau roluri sau multiplicități clare./ Relațiile dintre Order-OrderItem și OrderItem-Product au fost definite explicit.</t>
+  </si>
+  <si>
+    <t>DrinkShopController conține logică de business./ Controllerul a fost simplificat pentru a delega operațiile către DrinShopService.</t>
+  </si>
+  <si>
+    <t>Nu există o strategie clară de tratare a erorilor./ A fost introdusă ierarhia ApplicationException, ValidationException și StockException.</t>
+  </si>
+  <si>
+    <t>DrinkShopService centralizează prea multă logică./ Responsabilitățile au fost distribuite către OrderService, ProductService, RetetaService și StocService.</t>
+  </si>
+  <si>
+    <t>Arhitectura nu include gestionarea utilizatorilor și rolurilor (Administrator/Casier)./ Au fost adăugate clasele User și UserRole.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -386,78 +432,79 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -785,19 +832,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -821,10 +868,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="26"/>
+      <c r="E4" s="27"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -839,10 +886,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="28"/>
+      <c r="E5" s="29"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -858,19 +905,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1098,19 +1145,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1123,51 +1170,67 @@
       <c r="H3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="I3" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="23" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="D7" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1183,58 +1246,82 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
@@ -1379,19 +1466,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1411,10 +1498,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1425,10 +1512,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1440,15 +1527,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1697,19 +1784,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1729,8 +1816,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1741,8 +1828,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1754,8 +1841,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1985,11 +2072,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="35" t="s">
+      <c r="C32" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -1427,7 +1427,9 @@
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria-Melania\OneDrive\Documents\Proiect VVSS\VVSS-MyDrinkShop\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria-Melania\Desktop\vvss\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" tabRatio="650" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -172,74 +172,138 @@
     <t>Nu este specificat ce se întâmplă dacă ingredientele necesare pentru o băutură nu sunt disponibile în stoc.</t>
   </si>
   <si>
-    <t>Nu sunt specificate rolurile utilizatorilor (ex: administrator, casier.</t>
-  </si>
-  <si>
     <t>Nu este specificat dacă fișierele text sunt create automat la prima rulare.</t>
   </si>
   <si>
-    <t>Nu este clar dacă cantitatea afișară se referă la produsul final sau la ingredientele utilizate.</t>
+    <t>60 min</t>
+  </si>
+  <si>
+    <t>13.03.2026</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>Modelul inițial nu includea unitateea de măsură pentru ingrediente./A fost adăugat enum-ul UnitateMasura în relația cu IngredientReteta.</t>
+  </si>
+  <si>
+    <t>Unele relații nu aveau roluri sau multiplicități clare./ Relațiile dintre Order-OrderItem și OrderItem-Product au fost definite explicit.</t>
+  </si>
+  <si>
+    <t>DrinkShopController conține logică de business./ Controllerul a fost simplificat pentru a delega operațiile către DrinShopService.</t>
+  </si>
+  <si>
+    <t>Nu există o strategie clară de tratare a erorilor./ A fost introdusă ierarhia ApplicationException, ValidationException și StockException.</t>
+  </si>
+  <si>
+    <t>DrinkShopService centralizează prea multă logică./ Responsabilitățile au fost distribuite către OrderService, ProductService, RetetaService și StocService.</t>
+  </si>
+  <si>
+    <t>Arhitectura nu include gestionarea utilizatorilor și rolurilor (Administrator/Casier)./ Au fost adăugate clasele User și UserRole.</t>
+  </si>
+  <si>
+    <t>Se menționează Java și JavaFX, dar nu este specificată versiunea</t>
+  </si>
+  <si>
+    <t>Cerințele nu precizează pașii necesari pentru realizarea principalelor acțiuni (ex: adăugare produs, creare comandă)</t>
+  </si>
+  <si>
+    <t>Nu este specificat ce se întâmplă când se șterg date care sunt folosite în alte părți ale sistemului</t>
+  </si>
+  <si>
+    <t>Nu sunt specificate rolurile utilizatorilor (ex: administrator, casier)</t>
+  </si>
+  <si>
+    <t>Cerința funcțională 5</t>
+  </si>
+  <si>
+    <t>Cerința funcțională 2</t>
+  </si>
+  <si>
+    <t>Nu sunt definite toate atributele unui produs (ex: nume, preț).</t>
+  </si>
+  <si>
+    <t>Cerința non-funcțională 3</t>
+  </si>
+  <si>
+    <t>Cerințe non-funcțională 2</t>
+  </si>
+  <si>
+    <t>Cerințe non-funcțională 1</t>
+  </si>
+  <si>
+    <t>Cerința funcțională 3</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Linia 5</t>
   </si>
   <si>
     <t>Interfața este descrică ca fiind "intuitivă", dar nu sunt definite fluxurile de utilizare.</t>
   </si>
   <si>
-    <t>Se menționează Java și JavaFX, dar nu este specificată versiunea minimă necesară.</t>
-  </si>
-  <si>
-    <t>60 min</t>
-  </si>
-  <si>
-    <t>13.03.2026</t>
-  </si>
-  <si>
-    <t>A04</t>
-  </si>
-  <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>A08</t>
-  </si>
-  <si>
-    <t>A09</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>A03</t>
-  </si>
-  <si>
-    <t>Modelul inițial nu includea unitateea de măsură pentru ingrediente./A fost adăugat enum-ul UnitateMasura în relația cu IngredientReteta.</t>
-  </si>
-  <si>
-    <t>Unele relații nu aveau roluri sau multiplicități clare./ Relațiile dintre Order-OrderItem și OrderItem-Product au fost definite explicit.</t>
-  </si>
-  <si>
-    <t>DrinkShopController conține logică de business./ Controllerul a fost simplificat pentru a delega operațiile către DrinShopService.</t>
-  </si>
-  <si>
-    <t>Nu există o strategie clară de tratare a erorilor./ A fost introdusă ierarhia ApplicationException, ValidationException și StockException.</t>
-  </si>
-  <si>
-    <t>DrinkShopService centralizează prea multă logică./ Responsabilitățile au fost distribuite către OrderService, ProductService, RetetaService și StocService.</t>
-  </si>
-  <si>
-    <t>Arhitectura nu include gestionarea utilizatorilor și rolurilor (Administrator/Casier)./ Au fost adăugate clasele User și UserRole.</t>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>Clasele sunt denumite atât în limba română, cât și în limba engleză, ceea ce afectează consistența și claritatea rolului acestora.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -432,80 +496,99 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,7 +902,8 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="6" customWidth="1"/>
     <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
@@ -832,19 +916,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -868,10 +952,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="35"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -886,10 +970,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -905,19 +989,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -940,7 +1024,9 @@
       <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="26" t="s">
+        <v>64</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>44</v>
       </c>
@@ -951,11 +1037,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>65</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -963,12 +1051,14 @@
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2" t="s">
-        <v>46</v>
+      <c r="C12" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -976,12 +1066,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2" t="s">
-        <v>47</v>
+      <c r="C13" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -989,44 +1081,60 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
+      <c r="D17" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
@@ -1042,9 +1150,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
@@ -1060,36 +1168,36 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="15"/>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="3"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
@@ -1098,7 +1206,7 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
+      <c r="E25" s="24"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C27" s="11" t="s">
@@ -1106,7 +1214,7 @@
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1145,19 +1253,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1181,10 +1289,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="38"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1199,10 +1307,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="40"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1218,19 +1326,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="24"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="24"/>
+      <c r="D7" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="32"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1250,12 +1358,12 @@
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
+      <c r="C10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1263,12 +1371,12 @@
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
+      <c r="C11" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1276,12 +1384,12 @@
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
+      <c r="C12" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="31" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1289,12 +1397,12 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2" t="s">
-        <v>60</v>
+      <c r="C13" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="31" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1302,12 +1410,12 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
-        <v>59</v>
+      <c r="C14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="31" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1315,22 +1423,26 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+      <c r="C16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="31" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
@@ -1428,7 +1540,7 @@
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1468,19 +1580,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1500,10 +1612,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="41"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1514,10 +1626,10 @@
       <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="35"/>
+      <c r="E5" s="43"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1529,15 +1641,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1786,19 +1898,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
       <c r="H2" s="3"/>
       <c r="I2" s="19" t="s">
         <v>30</v>
@@ -1818,8 +1930,8 @@
       <c r="C4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
       <c r="H4" s="17" t="s">
         <v>21</v>
       </c>
@@ -1830,8 +1942,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
@@ -1843,8 +1955,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="20"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2074,11 +2186,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
       <c r="F32" s="18"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">
